--- a/outputs/LBSPR_Dtrunculus_Tablas.xlsx
+++ b/outputs/LBSPR_Dtrunculus_Tablas.xlsx
@@ -35,10 +35,10 @@
     <t xml:space="preserve">SPR_obs</t>
   </si>
   <si>
-    <t xml:space="preserve">SPR_MLS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPR_MLS25</t>
+    <t xml:space="preserve">SPR_MCRS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_MCRS25</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA_SPR_pp</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">DELTA_SPR_pct</t>
   </si>
   <si>
-    <t xml:space="preserve">MLS</t>
+    <t xml:space="preserve">MCRS</t>
   </si>
   <si>
     <t xml:space="preserve">N_replicas</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">FM</t>
   </si>
   <si>
-    <t xml:space="preserve">SPR_det_MLS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P_SPR40_MLS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPR_det_MLS25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P_SPR40_MLS25</t>
+    <t xml:space="preserve">SPR_det_MCRS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_SPR40_MCRS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_det_MCRS25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_SPR40_MCRS25</t>
   </si>
   <si>
     <t xml:space="preserve">Beneficio</t>
